--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Serbia SuperLiga_20242025.xlsx
@@ -63710,19 +63710,19 @@
         <v>2.58</v>
       </c>
       <c r="AU290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV290" t="n">
         <v>3</v>
       </c>
       <c r="AW290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX290" t="n">
         <v>4</v>
       </c>
       <c r="AY290" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ290" t="n">
         <v>7</v>
@@ -64146,22 +64146,22 @@
         <v>2.18</v>
       </c>
       <c r="AU292" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV292" t="n">
         <v>5</v>
       </c>
       <c r="AW292" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY292" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AZ292" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA292" t="n">
         <v>10</v>
@@ -64370,16 +64370,16 @@
         <v>7</v>
       </c>
       <c r="AW293" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX293" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AY293" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ293" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA293" t="n">
         <v>2</v>
@@ -64800,22 +64800,22 @@
         <v>3.07</v>
       </c>
       <c r="AU295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV295" t="n">
         <v>5</v>
       </c>
       <c r="AW295" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX295" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY295" t="n">
         <v>15</v>
       </c>
       <c r="AZ295" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA295" t="n">
         <v>6</v>
@@ -65018,22 +65018,22 @@
         <v>3.2</v>
       </c>
       <c r="AU296" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV296" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW296" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX296" t="n">
         <v>8</v>
       </c>
       <c r="AY296" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ296" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA296" t="n">
         <v>3</v>
@@ -65236,22 +65236,22 @@
         <v>2.74</v>
       </c>
       <c r="AU297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV297" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW297" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX297" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY297" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ297" t="n">
         <v>10</v>
-      </c>
-      <c r="AX297" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY297" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ297" t="n">
-        <v>13</v>
       </c>
       <c r="BA297" t="n">
         <v>6</v>
